--- a/results/predictions.xlsx
+++ b/results/predictions.xlsx
@@ -471,14 +471,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The listing states it is a former Co-op convenience store, vacant since relocation and offered with vacant possession. Per rules, “former” and “vacant possession” indicate it is not currently operating as a food store or any other category.</t>
+          <t>Listing states a former Co-op convenience store and vacant possession; current use is not operating. Terms like “former” and “vacant” trigger None under the rules, despite prior food retail fit-out and use.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -486,8 +486,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F2" s="2" t="b">
-        <v>0</v>
+      <c r="F2" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -501,14 +501,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Listing is for a plot of land/ancient woodland with potential for development subject to planning. No current operation as a nursery, SEN school, or food store is stated.</t>
+          <t>Current use is a plot of ancient woodland/land; no operating business and no connection to nursery, SEN school, or food retail. Phrases like “opportunity to build” indicate uncommitted use, triggering Medium confidence per rules.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -516,8 +516,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F3" s="1" t="b">
-        <v>0</v>
+      <c r="F3" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Currently fully let as general retail (ground/first floors) with a dance studio (second floor). No indication of a children’s nursery, SEN school, or a food retail store operating on site.</t>
+          <t>Currently fully let as a general retail premises with ancillary storage and a dance studio; no indication of a children’s nursery, SEN school, or food retail tenant. No “former”/vacant language. Therefore not in target sectors.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -561,14 +561,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Listing states it is a former café, the business has ceased trading, and the property is offered with vacant possession. Therefore it is not currently operating as a nursery, SEN school, or food store.</t>
+          <t>Listing states a former café that has ceased trading and is offered with vacant possession. No current nursery, SEN school, or food store operation. Presence of “suitable for”/future-use language warrants Medium confidence per rules.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -576,8 +576,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F5" s="1" t="b">
-        <v>0</v>
+      <c r="F5" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -591,14 +591,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Listing states it is a former doctor’s surgery and markets it as suitable for alternative uses; no current operation as nursery, SEN school, or food store. The term “former” triggers None per rules.</t>
+          <t>Described as a former doctor’s surgery with “ideal for” alternative uses; no current nursery, SEN school, or food store operation stated. Language indicates vacancy/uncommitted use.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -606,8 +606,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F6" s="2" t="b">
-        <v>0</v>
+      <c r="F6" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -628,7 +628,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The property’s current ground-floor use is a sunbed/tanning shop with a flat above, which is not a nursery, SEN school, or food store. The mention of a nearby Budgens/Premier store is location context and not the subject property.</t>
+          <t>Currently a ground-floor sunbed/tanning shop with a residential flat above. No nursery, SEN school, or food store operation. Nearby convenience store is only a location reference and not the subject property.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Currently operating as a retail shop manufacturing and selling bath products; not a food store, nursery, or SEN school. Current use stated explicitly.</t>
+          <t>Currently a mixed-use property with a retail shop/workshop selling bath products and a holiday apartment. Not a food retail store and not operating as a nursery or SEN school.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The listing is for a public house/freehouse (pub) currently in use as a licensed premises. This is not a nursery, SEN school, or food store, and there are no signals like “former” or “vacant possession” that would change current use.</t>
+          <t>The listing is for a public house/freehouse (pub) currently trading; this is unrelated to nurseries, SEN schools, or food retail. Nearby schools are location context only.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The listing is for a fully let multi-let industrial/trade park. Current use is industrial/trade units, not a nursery, SEN school, or a food retail store. Nearby occupiers mentioned are for location context only.</t>
+          <t>Current use is a fully let industrial/trade park with multiple industrial and trade counter units. No units operate as a nursery, SEN school, or a food retail store; occupiers listed are industrial/logistics (e.g., Royal Mail, DPD, De La Rue).</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Listing describes a fire door manufacturer/joinery business operating from an industrial property, not a nursery, SEN school, or food store.</t>
+          <t>Currently operates as an industrial fire door manufacturer/joinery business; not a nursery, SEN school, or food store.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>The asset for sale is a freehold with a long leasehold garage/workshop currently let; the ground-floor retail shop is sold off on a long lease. No current operation as a nursery, SEN school, or food store is stated. Nearby food retailers are only location context. Therefore none of the target sectors apply.</t>
+          <t>Current uses are a garage/workshop (let) and a ground-floor retail shop sold off on a long lease, plus flats. No mention of a nursery, SEN school, or a food retail tenant. Nearby Tesco Express is only a location reference. Development/airspace potential is irrelevant to current use.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -801,14 +801,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>The unit is a “blank canvas” marketed to healthcare/medical professionals with refurbishments completing by Aug 2026 and no named current tenant. Language is “suitable for”/versatile space, indicating no current operation. Nearby/adjacent Co-op and other park tenants are not this unit. Therefore it is not currently a nursery, SEN school, or food store.</t>
+          <t>Marketed as a blank-canvas healthcare/medical premises with no named current tenant and no active nursery, SEN school, or food store use. Language like “opportunity for Healthcare and Medical Professionals” and versatile space indicates uncommitted current use; adjacency to Co-Op is just location.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -816,8 +816,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F13" s="2" t="b">
-        <v>0</v>
+      <c r="F13" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -838,7 +838,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>The listing explicitly states it is currently let to and operated by an independent special educational needs provider and is "currently operating as independent SEN school," with an active lease (c. 11 years unexpired). The mention of "former grammar school" refers to historic use, not current use.</t>
+          <t>Explicitly stated as currently let to and operated by an independent special educational needs provider; listing says ‘Currently operating as independent SEN school’ with 11 years unexpired on the lease. ‘Former grammar school’ refers to historic use, not current.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Currently let to a vape/e-cigarette retailer and a hairdressing salon, with residential flats above. No childcare, SEN education, or food retail operation, and the listing explicitly notes no consent for those uses.</t>
+          <t>Currently let to a vape/e-cigarette retailer and a hairdressing salon with no consent for childcare, education, or food retail. These uses are unrelated to nursery, SEN school, or food store.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -891,14 +891,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Currently operating as a car showroom with attached residence; mentions of being ideal for other uses are speculative. Not a nursery, SEN school, or food store.</t>
+          <t>Currently a car showroom with residence; no nursery, SEN school, or food retail operation. Mentions “suitable for” other uses but no named current tenant in target sectors, so classify as None and flag Medium due to the ‘suitable for’ language.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -906,8 +906,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F16" s="2" t="b">
-        <v>0</v>
+      <c r="F16" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -928,7 +928,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>The listing explicitly describes an established, currently operating children’s day nursery (registered for 75, Good Ofsted, open year-round, currently at ~50% occupancy). No “former” or vacancy language present.</t>
+          <t>Listing explicitly describes an established, currently operating children’s day nursery (registered for 75, Good Ofsted, open year-round, staffed and trading).</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -951,14 +951,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Listing states “Vacant FREEHOLD Nursery Building” and “offered with full vacant possession.” Per rule 2, these phrases signal None, regardless of nursery configuration or past operation.</t>
+          <t>Listing states “Vacant FREEHOLD Nursery Building” and “will be offered with full vacant possession,” which per Rule 2 signals None, despite mentioning it is currently configured/operated as a nursery. Strong nursery connection but being sold vacant merits Medium confidence.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -966,8 +966,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F18" s="2" t="b">
-        <v>0</v>
+      <c r="F18" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -981,14 +981,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>This is an airspace development opportunity to build apartments; per rule 5 we classify what is being sold (airspace), not the underlying tenant. Although the ground floor is let to Sainsbury’s, the listing is for the rooftop development rights, not a currently operating food store.</t>
+          <t>This is a sale of airspace development rights to create apartments. Although the ground floor is let to Sainsbury’s (a food store), Rule 5 says classify what is being sold—the airspace—so it is not a current target-sector use. Confidence is Medium because it involves airspace above a target-sector tenant.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -996,8 +996,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F19" s="2" t="b">
-        <v>0</v>
+      <c r="F19" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Industrial/warehouse complex marketed for manufacturing/storage uses; no indication of current operation as nursery, SEN school, or food store. Language like “suitable for” confirms not currently in those sectors.</t>
+          <t>Industrial/warehouse complex with uses for manufacturing, storage, engineering, and distribution. No current operation as a nursery, SEN school, or food retail store; clearly unrelated to target sectors.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1041,14 +1041,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>The listing states the property is offered with full vacant possession and is a vacant freehold nursery building. Despite nursery fit-out, it is not currently operating. Per Rule 2, “vacant possession” signals None.</t>
+          <t>Listing states “Vacant FREEHOLD Nursery Building” and “offered…with full vacant possession,” so it is not currently operating. Despite nursery fit-out and sector language, current use is vacant per Rule 2.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1056,8 +1056,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F21" s="2" t="b">
-        <v>0</v>
+      <c r="F21" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Listing explicitly states the unit is used as a small convenience store and is let on a current lease with the business remaining unaffected, confirming current food retail operation.</t>
+          <t>Listing states the unit is currently used as a small convenience store and is let on a 9-year FRI lease with the business remaining unaffected by the sale, confirming active food retail use.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1101,14 +1101,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>The listing states the unit is vacant and ‘most recently trading as’ a nursery with the operator’s ‘lease expired’. These phrases explicitly indicate it is not currently operating. Despite D1 consent and nursery fit-out, this is marketing/suitability, not current use.</t>
+          <t>Listing states the unit is vacant and ‘most recently trading as’ a nursery with the operator’s ‘lease expired’—phrases that signal None under the rules. D1 nursery consent and retained nursery fit-out indicate former/suitable use, not current operation.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1116,8 +1116,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F23" s="2" t="b">
-        <v>0</v>
+      <c r="F23" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1131,14 +1131,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>The listing repeatedly states it is a former Costcutter supermarket and will be sold vacant. Per rules, terms like “former” and “vacant” mean it is not currently operating as a food store or other target use.</t>
+          <t>Described repeatedly as a former Costcutter supermarket, sold vacant with no lease/third-party agreements and “suitable for alternative uses.” Current use is not an operating food store.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1146,8 +1146,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F24" s="2" t="b">
-        <v>0</v>
+      <c r="F24" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/results/predictions.xlsx
+++ b/results/predictions.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Food Store</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -478,15 +478,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Listing states a former Co-op convenience store and vacant possession; current use is not operating. Terms like “former” and “vacant” trigger None under the rules, despite prior food retail fit-out and use.</t>
+          <t>Explicitly a former Co-op convenience store with retained food-retail fit-out (chillers, shelving) and A1 use; vacant but clearly food retail. Former/vacant target-sector use triggers Medium confidence.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="b">
+          <t>Food Store</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -501,14 +501,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Current use is a plot of ancient woodland/land; no operating business and no connection to nursery, SEN school, or food retail. Phrases like “opportunity to build” indicate uncommitted use, triggering Medium confidence per rules.</t>
+          <t>Listing is for a plot of ancient woodland/land with generic development potential. No current or former use as a nursery, SEN school, or food store is mentioned.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -516,8 +516,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F3" s="2" t="b">
-        <v>1</v>
+      <c r="F3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Currently fully let as a general retail premises with ancillary storage and a dance studio; no indication of a children’s nursery, SEN school, or food retail tenant. No “former”/vacant language. Therefore not in target sectors.</t>
+          <t>Listing is a generic retail investment (ground-floor retail with storage; second-floor dance studio). No mention of nursery, SEN school, or food store current/former use or consent.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -546,7 +546,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F4" s="1" t="b">
+      <c r="F4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Listing states a former café that has ceased trading and is offered with vacant possession. No current nursery, SEN school, or food store operation. Presence of “suitable for”/future-use language warrants Medium confidence per rules.</t>
+          <t>Former café with residential above; no mention of nursery, SEN school, or food retail store use. “Suitable for a variety of uses” language does not qualify for target sectors. Therefore not relevant to Nursery/SEN/Food Store.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -576,7 +576,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F5" s="2" t="b">
+      <c r="F5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Described as a former doctor’s surgery with “ideal for” alternative uses; no current nursery, SEN school, or food store operation stated. Language indicates vacancy/uncommitted use.</t>
+          <t>Former doctor’s surgery with generic ‘alternative uses’ language and no mention of nursery, SEN school, or food store use or consent.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -606,7 +606,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F6" s="1" t="b">
+      <c r="F6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Currently a ground-floor sunbed/tanning shop with a residential flat above. No nursery, SEN school, or food store operation. Nearby convenience store is only a location reference and not the subject property.</t>
+          <t>The property is a tanning/sunbed shop with a residential flat above. No current or former nursery, SEN school, or food store use is indicated. Mention of a nearby Budgens/Premier is location context only and not the subject property.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -636,7 +636,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F7" s="1" t="b">
+      <c r="F7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -651,14 +651,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Currently a mixed-use property with a retail shop/workshop selling bath products and a holiday apartment. Not a food retail store and not operating as a nursery or SEN school.</t>
+          <t>Retail shop selling bath products with a holiday apartment; no indication of nursery, SEN, or food retail use. Generic suitability language (“could be used for a new retail business”) present, so classify as None with Medium confidence.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -666,8 +666,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F8" s="1" t="b">
-        <v>0</v>
+      <c r="F8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The listing is for a public house/freehouse (pub) currently trading; this is unrelated to nurseries, SEN schools, or food retail. Nearby schools are location context only.</t>
+          <t>Listing is a Grade II listed pub/freehouse with accommodation and trade garden. No current or former use as a nursery, SEN school, or food store is mentioned. Nearby schools are irrelevant per rules. Therefore not acquisition-relevant to target sectors.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -696,7 +696,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F9" s="1" t="b">
+      <c r="F9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Current use is a fully let industrial/trade park with multiple industrial and trade counter units. No units operate as a nursery, SEN school, or a food retail store; occupiers listed are industrial/logistics (e.g., Royal Mail, DPD, De La Rue).</t>
+          <t>Multi-let industrial/trade park investment with industrial/trade counter units; no current or former use as nursery, SEN school, or food retail mentioned, and no suitability language for those sectors.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -726,7 +726,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F10" s="1" t="b">
+      <c r="F10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Currently operates as an industrial fire door manufacturer/joinery business; not a nursery, SEN school, or food store.</t>
+          <t>Industrial business sale of a fire door manufacturer/joinery operating from a freehold industrial property; no current or former use as nursery, SEN school, or food store, and no sector-specific suitability language.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -756,7 +756,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F11" s="1" t="b">
+      <c r="F11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Current uses are a garage/workshop (let) and a ground-floor retail shop sold off on a long lease, plus flats. No mention of a nursery, SEN school, or a food retail tenant. Nearby Tesco Express is only a location reference. Development/airspace potential is irrelevant to current use.</t>
+          <t>Investment sale of freehold with long-lease shop and garage/workshop; no mention of nursery, SEN school, or food retail use for the subject property. Nearby Tesco Express is only a location reference.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -786,7 +786,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F12" s="1" t="b">
+      <c r="F12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Marketed as a blank-canvas healthcare/medical premises with no named current tenant and no active nursery, SEN school, or food store use. Language like “opportunity for Healthcare and Medical Professionals” and versatile space indicates uncommitted current use; adjacency to Co-Op is just location.</t>
+          <t>Listing is for a healthcare/medical clinic space with treatment rooms and rehab area, not a nursery, SEN school, or food store. The nearby Co-Op is only a location reference and should be ignored. Contains “variety of businesses”/marketed-to-professionals language, triggering Medium confidence per rules.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -816,7 +816,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F13" s="1" t="b">
+      <c r="F13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -831,14 +831,14 @@
           <t>SEN School</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Explicitly stated as currently let to and operated by an independent special educational needs provider; listing says ‘Currently operating as independent SEN school’ with 11 years unexpired on the lease. ‘Former grammar school’ refers to historic use, not current.</t>
+          <t>Currently let to and operated by an independent special educational needs provider with F1 (formerly D1) consent and sector-specific facilities; thus clearly an SEN School. Confidence set to Medium due to explicit mention of planning consent (a Medium trigger).</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -846,8 +846,8 @@
           <t>SEN School</t>
         </is>
       </c>
-      <c r="F14" s="1" t="b">
-        <v>0</v>
+      <c r="F14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -868,7 +868,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Currently let to a vape/e-cigarette retailer and a hairdressing salon with no consent for childcare, education, or food retail. These uses are unrelated to nursery, SEN school, or food store.</t>
+          <t>Two ground-floor units let to a vape shop and hairdresser with A1/A2 consent; upper floors are residential. No current or former nursery, SEN, or food retail use or consent is indicated.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -876,7 +876,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F15" s="1" t="b">
+      <c r="F15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Currently a car showroom with residence; no nursery, SEN school, or food retail operation. Mentions “suitable for” other uses but no named current tenant in target sectors, so classify as None and flag Medium due to the ‘suitable for’ language.</t>
+          <t>Car showroom with residence; no current or former use as nursery, SEN school, or food store. Only generic suitability language for alternative uses is given, which does not qualify. Suitability phrasing triggers Medium confidence.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -906,7 +906,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F16" s="1" t="b">
+      <c r="F16" t="b">
         <v>1</v>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Listing explicitly describes an established, currently operating children’s day nursery (registered for 75, Good Ofsted, open year-round, staffed and trading).</t>
+          <t>Listing is an operating children’s day nursery (registered for 75, Ofsted Good) being sold as a going concern. This directly matches the Nursery sector.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -936,7 +936,7 @@
           <t>Nursery</t>
         </is>
       </c>
-      <c r="F17" s="1" t="b">
+      <c r="F17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Nursery</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -958,15 +958,15 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Listing states “Vacant FREEHOLD Nursery Building” and “will be offered with full vacant possession,” which per Rule 2 signals None, despite mentioning it is currently configured/operated as a nursery. Strong nursery connection but being sold vacant merits Medium confidence.</t>
+          <t>Explicitly a nursery property (“Vacant FREEHOLD Nursery Building”; currently configured/operated as a nursery, Use Class E) offered with vacant possession. Listing also includes “suitable for a range of uses” language, which sets confidence to Medium per rules.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="b">
+          <t>Nursery</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
         <v>1</v>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>This is a sale of airspace development rights to create apartments. Although the ground floor is let to Sainsbury’s (a food store), Rule 5 says classify what is being sold—the airspace—so it is not a current target-sector use. Confidence is Medium because it involves airspace above a target-sector tenant.</t>
+          <t>This is an airspace development sale to create residential apartments. Although the ground floor is let to Sainsbury’s (food store), rule 5 says classify what is being sold—airspace/residential rights—so it’s not a target sector asset. Confidence is Medium due to airspace above a target-sector tenant.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -996,7 +996,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F19" s="1" t="b">
+      <c r="F19" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1011,14 +1011,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Industrial/warehouse complex with uses for manufacturing, storage, engineering, and distribution. No current operation as a nursery, SEN school, or food retail store; clearly unrelated to target sectors.</t>
+          <t>Industrial/warehouse complex with uses listed as manufacturing, storage, engineering and distribution. No current or former nursery, SEN school, or food store use mentioned. Presence of generic “suitable for” language triggers Medium confidence per rules.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1026,8 +1026,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F20" s="1" t="b">
-        <v>0</v>
+      <c r="F20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Nursery</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -1048,15 +1048,15 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Listing states “Vacant FREEHOLD Nursery Building” and “offered…with full vacant possession,” so it is not currently operating. Despite nursery fit-out and sector language, current use is vacant per Rule 2.</t>
+          <t>Vacant freehold property currently configured and fitted out as a children’s nursery (enclosed play areas, nursery-specific fit-out), marketed to the nursery sector. Listing also mentions variety of future uses, which sets confidence to Medium per rules.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="b">
+          <t>Nursery</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Listing states the unit is currently used as a small convenience store and is let on a 9-year FRI lease with the business remaining unaffected by the sale, confirming active food retail use.</t>
+          <t>Listing explicitly states the unit is used as a small convenience store (food retail) and is let on a lease. No alternative-use language or former use; clearly a food retail operation.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1086,7 +1086,7 @@
           <t>Food Store</t>
         </is>
       </c>
-      <c r="F22" s="1" t="b">
+      <c r="F22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Nursery</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -1108,15 +1108,15 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Listing states the unit is vacant and ‘most recently trading as’ a nursery with the operator’s ‘lease expired’—phrases that signal None under the rules. D1 nursery consent and retained nursery fit-out indicate former/suitable use, not current operation.</t>
+          <t>Vacant unit with existing D1 consent specifically for a children’s day nursery, formerly trading as a nursery and retaining nursery-specific fit-out (low-level sinks, play area). Clear sector relevance to Nursery. Confidence set to Medium per rule due to former/vacant use and suitability language.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="b">
+          <t>Nursery</t>
+        </is>
+      </c>
+      <c r="F23" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Food Store</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Described repeatedly as a former Costcutter supermarket, sold vacant with no lease/third-party agreements and “suitable for alternative uses.” Current use is not an operating food store.</t>
+          <t>Explicitly described as a former Costcutter supermarket (former food retail use), which qualifies under Rule 3. Listing also contains “suitable for a variety of alternative uses,” triggering Medium confidence.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="b">
+          <t>Food Store</t>
+        </is>
+      </c>
+      <c r="F24" t="b">
         <v>1</v>
       </c>
     </row>

--- a/results/predictions.xlsx
+++ b/results/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,11 +454,6 @@
           <t>manual_categorisation</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>requires_human_review</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -478,16 +473,13 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Explicitly a former Co-op convenience store with retained food-retail fit-out (chillers, shelving) and A1 use; vacant but clearly food retail. Former/vacant target-sector use triggers Medium confidence.</t>
+          <t>Former Co-op convenience store with retained food-retail fit-out (chillers, shelving) and A1 use; vacant former use in target sector qualifies as Food Store.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Food Store</t>
         </is>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +500,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Listing is for a plot of ancient woodland/land with generic development potential. No current or former use as a nursery, SEN school, or food store is mentioned.</t>
+          <t>Listing is for an acre-plus plot of ancient woodland/land with potential for an eco-home subject to planning. No current or former use as a nursery, SEN school, or food store is indicated; nearby amenities are irrelevant per rules.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -538,16 +527,13 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Listing is a generic retail investment (ground-floor retail with storage; second-floor dance studio). No mention of nursery, SEN school, or food store current/former use or consent.</t>
+          <t>Fully let high street property with ground-floor retail and a dance studio above; no mention of nursery/SEN use or food retail (convenience store/supermarket). Generic retail only.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F4" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -568,16 +554,13 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Former café with residential above; no mention of nursery, SEN school, or food retail store use. “Suitable for a variety of uses” language does not qualify for target sectors. Therefore not relevant to Nursery/SEN/Food Store.</t>
+          <t>Property is a former café with residential above; no indication of current or former nursery, SEN school, or food retail store use. Mentions of nearby Co-Op are location context only. Listing also uses ‘variety of alternative uses’ language, triggering Medium confidence.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -598,16 +581,13 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Former doctor’s surgery with generic ‘alternative uses’ language and no mention of nursery, SEN school, or food store use or consent.</t>
+          <t>Former doctor’s surgery with generic suitability/alternative-use language and no mention of nursery, SEN school, or food retail use. Therefore not sector-relevant. Confidence Medium due to presence of suitability phrasing.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -628,16 +608,13 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The property is a tanning/sunbed shop with a residential flat above. No current or former nursery, SEN school, or food store use is indicated. Mention of a nearby Budgens/Premier is location context only and not the subject property.</t>
+          <t>Ground floor sunbed/tanning shop with a residential flat above; no current or former nursery, SEN school, or food retail use. Reference to a nearby Budgens/Premier store is just location context and not the subject property.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F7" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -658,16 +635,13 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Retail shop selling bath products with a holiday apartment; no indication of nursery, SEN, or food retail use. Generic suitability language (“could be used for a new retail business”) present, so classify as None with Medium confidence.</t>
+          <t>Mixed-use property with a retail shop selling bath products and a holiday apartment. No indication of nursery, SEN school, or food retail use. The phrase “could be used for a new retail business” triggers the Medium confidence rule for suitability language.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -688,16 +662,13 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Listing is a Grade II listed pub/freehouse with accommodation and trade garden. No current or former use as a nursery, SEN school, or food store is mentioned. Nearby schools are irrelevant per rules. Therefore not acquisition-relevant to target sectors.</t>
+          <t>The listing is a Grade II listed public house (freehouse) with accommodation and trade garden. There is no mention of current or former use as a nursery, SEN school, or food retail store, nor any sector-specific consents or fit-out.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F9" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -718,16 +689,13 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Multi-let industrial/trade park investment with industrial/trade counter units; no current or former use as nursery, SEN school, or food retail mentioned, and no suitability language for those sectors.</t>
+          <t>Multi-let industrial/trade park investment with 15 industrial/trade counter units; no current or former use as nursery, SEN school, or food retail, and no sector-specific suitability language.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -748,16 +716,13 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Industrial business sale of a fire door manufacturer/joinery operating from a freehold industrial property; no current or former use as nursery, SEN school, or food store, and no sector-specific suitability language.</t>
+          <t>Industrial premises for a fire door manufacturing and joinery business; no mention of nursery, SEN school, or food store current/former use, and no suitability language indicating these sectors.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F11" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -778,16 +743,13 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Investment sale of freehold with long-lease shop and garage/workshop; no mention of nursery, SEN school, or food retail use for the subject property. Nearby Tesco Express is only a location reference.</t>
+          <t>Listing is a freehold investment comprising flats, a generic retail shop (sold off on long lease), and a leased workshop/garage with airspace development potential. No indication of current or former use as a nursery, SEN school, or food store. Nearby Tesco Express is only a location reference and should be ignored per rules.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -808,16 +770,13 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Listing is for a healthcare/medical clinic space with treatment rooms and rehab area, not a nursery, SEN school, or food store. The nearby Co-Op is only a location reference and should be ignored. Contains “variety of businesses”/marketed-to-professionals language, triggering Medium confidence per rules.</t>
+          <t>Healthcare/medical clinic-style unit with treatment rooms; no mention of current or former nursery, SEN school, or food retail use. Listing contains suitability/versatility language (“for Medical or Healthcare Professionals,” “variety of businesses”), which triggers Medium confidence.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -838,16 +797,13 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Currently let to and operated by an independent special educational needs provider with F1 (formerly D1) consent and sector-specific facilities; thus clearly an SEN School. Confidence set to Medium due to explicit mention of planning consent (a Medium trigger).</t>
+          <t>Explicitly described as an independent SEN school currently operating on site with F1 (formerly D1) consent, including specialist facilities (sensory/therapy suite).</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>SEN School</t>
         </is>
-      </c>
-      <c r="F14" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -868,16 +824,13 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Two ground-floor units let to a vape shop and hairdresser with A1/A2 consent; upper floors are residential. No current or former nursery, SEN, or food retail use or consent is indicated.</t>
+          <t>Retail units are let to a vape shop and a hairdresser with residential flats above. No current or former nursery/SEN/food store use and explicitly no consent for childcare/education or food retail. No sector-specific relevance.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F15" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -898,16 +851,13 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Car showroom with residence; no current or former use as nursery, SEN school, or food store. Only generic suitability language for alternative uses is given, which does not qualify. Suitability phrasing triggers Medium confidence.</t>
+          <t>Currently a car showroom with residence; no mention of nursery, SEN school, or food store current/former use or consent. Only generic ‘suitable for variety of uses’ language, which does not qualify for any target sector.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -928,16 +878,13 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Listing is an operating children’s day nursery (registered for 75, Ofsted Good) being sold as a going concern. This directly matches the Nursery sector.</t>
+          <t>Currently operating children’s day nursery with Ofsted rating and registration for 75 children; explicit active nursery use.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>Nursery</t>
         </is>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -958,16 +905,13 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Explicitly a nursery property (“Vacant FREEHOLD Nursery Building”; currently configured/operated as a nursery, Use Class E) offered with vacant possession. Listing also includes “suitable for a range of uses” language, which sets confidence to Medium per rules.</t>
+          <t>Listing explicitly describes a freehold property currently configured/operated as a nursery and being sold with vacant possession. This is directly relevant to Nursery acquisitions. Presence of vacancy and “suitable for a range of uses” language triggers Medium confidence per rules.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Nursery</t>
         </is>
-      </c>
-      <c r="F18" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -988,16 +932,13 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>This is an airspace development sale to create residential apartments. Although the ground floor is let to Sainsbury’s (food store), rule 5 says classify what is being sold—airspace/residential rights—so it’s not a target sector asset. Confidence is Medium due to airspace above a target-sector tenant.</t>
+          <t>This is an airspace development sale to build residential apartments; per Rule 5 we classify what is being sold, not the underlying Sainsbury’s tenant. Therefore not acquisition-relevant to Nursery, SEN School, or Food Store. Airspace above a target-sector tenant triggers Medium confidence.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F19" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1018,16 +959,13 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Industrial/warehouse complex with uses listed as manufacturing, storage, engineering and distribution. No current or former nursery, SEN school, or food store use mentioned. Presence of generic “suitable for” language triggers Medium confidence per rules.</t>
+          <t>Industrial/warehouse complex with uses listed as manufacturing, storage, engineering and distribution; no mention of nursery, SEN school, or food store current or former use. Presence of “suitable for” language triggers Medium confidence.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
-      </c>
-      <c r="F20" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1048,16 +986,13 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Vacant freehold property currently configured and fitted out as a children’s nursery (enclosed play areas, nursery-specific fit-out), marketed to the nursery sector. Listing also mentions variety of future uses, which sets confidence to Medium per rules.</t>
+          <t>Listing is a vacant freehold property currently configured and fitted as a children’s nursery with enclosed play areas and nursery-specific fit-out. Although it mentions alternative uses, it is clearly a former/configured nursery, which qualifies.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Nursery</t>
         </is>
-      </c>
-      <c r="F21" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1078,16 +1013,13 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Listing explicitly states the unit is used as a small convenience store (food retail) and is let on a lease. No alternative-use language or former use; clearly a food retail operation.</t>
+          <t>Listing explicitly describes the property as a retail unit used as a small convenience store with an ongoing lease, indicating current food retail use.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Food Store</t>
         </is>
-      </c>
-      <c r="F22" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1108,16 +1040,13 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Vacant unit with existing D1 consent specifically for a children’s day nursery, formerly trading as a nursery and retaining nursery-specific fit-out (low-level sinks, play area). Clear sector relevance to Nursery. Confidence set to Medium per rule due to former/vacant use and suitability language.</t>
+          <t>Vacant former children’s day nursery with D1 nursery consent and retained nursery-specific fit-out (low-level sinks, kitchen, secure outdoor play area). Meets sector relevance for Nursery. Confidence set to Medium due to former/vacant use and “suitable for” language.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>Nursery</t>
         </is>
-      </c>
-      <c r="F23" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1138,16 +1067,13 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Explicitly described as a former Costcutter supermarket (former food retail use), which qualifies under Rule 3. Listing also contains “suitable for a variety of alternative uses,” triggering Medium confidence.</t>
+          <t>The listing explicitly describes a “Former Costcutter supermarket,” which is a food retail use. Former food store use qualifies as Food Store even if now vacant. The text also includes “suitable for a variety of alternative uses,” which triggers Medium confidence.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Food Store</t>
         </is>
-      </c>
-      <c r="F24" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
